--- a/data/trans_orig/P34A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2007</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>473457</t>
+          <t>472880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>534661</t>
+          <t>536400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>635503</t>
+          <t>638055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>707950</t>
+          <t>710051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1130134</t>
+          <t>1129073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1222320</t>
+          <t>1227420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480220</t>
+          <t>478481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>541424</t>
+          <t>542001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585177</t>
+          <t>583076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657624</t>
+          <t>655072</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1085688</t>
+          <t>1080588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1177874</t>
+          <t>1178935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634746</t>
+          <t>636031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>719988</t>
+          <t>717090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>637248</t>
+          <t>642124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>719453</t>
+          <t>719467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1295256</t>
+          <t>1298427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1410719</t>
+          <t>1410523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>949876</t>
+          <t>952774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1035118</t>
+          <t>1033833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>840266</t>
+          <t>840252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>922471</t>
+          <t>917595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1818864</t>
+          <t>1819060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1934327</t>
+          <t>1931156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>128540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168937</t>
+          <t>173276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158186</t>
+          <t>158789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202626</t>
+          <t>199821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296421</t>
+          <t>296905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359776</t>
+          <t>359422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377881</t>
+          <t>373542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>420625</t>
+          <t>418278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263287</t>
+          <t>266092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307727</t>
+          <t>307124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652955</t>
+          <t>653309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>716310</t>
+          <t>715826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1277681</t>
+          <t>1269057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1384498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1471330</t>
+          <t>1475908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1592159</t>
+          <t>1591174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2777688</t>
+          <t>2775725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2943935</t>
+          <t>2940722</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1844093</t>
+          <t>1847065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1953882</t>
+          <t>1962506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1726600</t>
+          <t>1727585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1847429</t>
+          <t>1842851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3606387</t>
+          <t>3609600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3772634</t>
+          <t>3774597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2012</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225108</t>
+          <t>223727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>277762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>446170</t>
+          <t>450354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>522760</t>
+          <t>523911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>694340</t>
+          <t>689702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>777762</t>
+          <t>784902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>694169</t>
+          <t>695984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748638</t>
+          <t>750019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>813939</t>
+          <t>812788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>890529</t>
+          <t>886345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1532683</t>
+          <t>1525543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1616105</t>
+          <t>1620743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>411651</t>
+          <t>410198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>489726</t>
+          <t>489969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>493384</t>
+          <t>493071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>570929</t>
+          <t>571957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>927153</t>
+          <t>923247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1038157</t>
+          <t>1033916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1473370</t>
+          <t>1473127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1551445</t>
+          <t>1552898</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1186874</t>
+          <t>1185846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1264419</t>
+          <t>1264732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2682742</t>
+          <t>2686983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2793746</t>
+          <t>2797652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>50836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83644</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67353</t>
+          <t>67113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101741</t>
+          <t>101668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125761</t>
+          <t>126848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171791</t>
+          <t>174284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>397537</t>
+          <t>398554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429702</t>
+          <t>430345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356890</t>
+          <t>356963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391278</t>
+          <t>391518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>768022</t>
+          <t>765529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814052</t>
+          <t>812965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>716600</t>
+          <t>721725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>819659</t>
+          <t>821006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1040181</t>
+          <t>1042616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1159173</t>
+          <t>1154525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1786660</t>
+          <t>1793730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1937543</t>
+          <t>1944759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2598365</t>
+          <t>2597018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2701424</t>
+          <t>2696299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2393959</t>
+          <t>2398607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2512951</t>
+          <t>2510516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5033613</t>
+          <t>5026397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5184496</t>
+          <t>5177426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2016</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>327570</t>
+          <t>328363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382879</t>
+          <t>381874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>527476</t>
+          <t>528798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>593572</t>
+          <t>593866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>871467</t>
+          <t>878087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>957900</t>
+          <t>958231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371468</t>
+          <t>372473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426777</t>
+          <t>425984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401088</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467184</t>
+          <t>465862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>791107</t>
+          <t>790776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>877540</t>
+          <t>870920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,8%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>620776</t>
+          <t>618059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>709492</t>
+          <t>708822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>751145</t>
+          <t>746579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>837587</t>
+          <t>835102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1393708</t>
+          <t>1395403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1520251</t>
+          <t>1515975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1366893</t>
+          <t>1367563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1455609</t>
+          <t>1458326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1150713</t>
+          <t>1153198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1237155</t>
+          <t>1241721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2544434</t>
+          <t>2548710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2670977</t>
+          <t>2669282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106558</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146048</t>
+          <t>147545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135158</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180909</t>
+          <t>177786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250615</t>
+          <t>254448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313715</t>
+          <t>312730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400838</t>
+          <t>399341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440328</t>
+          <t>441243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>368231</t>
+          <t>371354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>413982</t>
+          <t>412636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>782312</t>
+          <t>783297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>845412</t>
+          <t>841579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1091393</t>
+          <t>1089899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1198720</t>
+          <t>1200840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1441704</t>
+          <t>1445027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1569618</t>
+          <t>1565189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2570205</t>
+          <t>2570666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2727966</t>
+          <t>2729724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2178898</t>
+          <t>2176778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2286225</t>
+          <t>2287719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1962482</t>
+          <t>1966911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2090396</t>
+          <t>2087073</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4181752</t>
+          <t>4179994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4339513</t>
+          <t>4339052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2023</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243316</t>
+          <t>242348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284892</t>
+          <t>283405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>436058</t>
+          <t>434511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>475885</t>
+          <t>476273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687830</t>
+          <t>686643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>744130</t>
+          <t>746146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226539</t>
+          <t>228026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268115</t>
+          <t>269083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273708</t>
+          <t>273320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313535</t>
+          <t>315082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>514878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573194</t>
+          <t>574381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>428924</t>
+          <t>453954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>740283</t>
+          <t>744729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>550071</t>
+          <t>561571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>865965</t>
+          <t>866077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1145335</t>
+          <t>1126116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1567990</t>
+          <t>1592285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1545331</t>
+          <t>1540885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1856690</t>
+          <t>1831660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1369624</t>
+          <t>1369512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1685518</t>
+          <t>1674018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2953212</t>
+          <t>2928917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3375867</t>
+          <t>3395086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>128283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174601</t>
+          <t>175882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154468</t>
+          <t>155106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193801</t>
+          <t>194929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>292354</t>
+          <t>295167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353549</t>
+          <t>356072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470973</t>
+          <t>469692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515432</t>
+          <t>517291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>466285</t>
+          <t>465157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505618</t>
+          <t>504980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>952111</t>
+          <t>949588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1013306</t>
+          <t>1010493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>781516</t>
+          <t>823313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1162127</t>
+          <t>1170032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1165871</t>
+          <t>1163248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1500338</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2095982</t>
+          <t>2087516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2616851</t>
+          <t>2627564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2280491</t>
+          <t>2272586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2661102</t>
+          <t>2619305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2144930</t>
+          <t>2135841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2479397</t>
+          <t>2482020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4471035</t>
+          <t>4460322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4991904</t>
+          <t>5000370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>472880</t>
+          <t>473110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>536400</t>
+          <t>535252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>638055</t>
+          <t>640641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>710051</t>
+          <t>711258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1129073</t>
+          <t>1131113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1227420</t>
+          <t>1222782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478481</t>
+          <t>479629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>542001</t>
+          <t>541771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>583076</t>
+          <t>581869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655072</t>
+          <t>652486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1080588</t>
+          <t>1085226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1178935</t>
+          <t>1176895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>636031</t>
+          <t>635254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>717090</t>
+          <t>716991</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>642124</t>
+          <t>639499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>719467</t>
+          <t>718132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1298427</t>
+          <t>1298559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1410523</t>
+          <t>1409638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>952774</t>
+          <t>952873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1033833</t>
+          <t>1034610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>840252</t>
+          <t>841587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>917595</t>
+          <t>920220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1819060</t>
+          <t>1819945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1931156</t>
+          <t>1931024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128540</t>
+          <t>126197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173276</t>
+          <t>169560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158789</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199821</t>
+          <t>203958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296905</t>
+          <t>297206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359422</t>
+          <t>357533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>373542</t>
+          <t>377258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418278</t>
+          <t>420621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266092</t>
+          <t>261955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307124</t>
+          <t>305813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653309</t>
+          <t>655198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>715826</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1269057</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1384498</t>
+          <t>1378935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1475908</t>
+          <t>1472231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1591174</t>
+          <t>1591192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2775725</t>
+          <t>2778487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2940722</t>
+          <t>2944256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1847065</t>
+          <t>1852628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1962506</t>
+          <t>1965320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1727585</t>
+          <t>1727567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1842851</t>
+          <t>1846528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3609600</t>
+          <t>3606066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3774597</t>
+          <t>3771835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>223727</t>
+          <t>223853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>277762</t>
+          <t>279434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>450354</t>
+          <t>452419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>523911</t>
+          <t>524013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>689702</t>
+          <t>688118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>784902</t>
+          <t>780820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695984</t>
+          <t>694312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>750019</t>
+          <t>749893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>812788</t>
+          <t>812686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>886345</t>
+          <t>884280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1525543</t>
+          <t>1529625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1620743</t>
+          <t>1622327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,22%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>410198</t>
+          <t>411600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>489969</t>
+          <t>491841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>493071</t>
+          <t>492753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>571957</t>
+          <t>571204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>923247</t>
+          <t>919325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1033916</t>
+          <t>1033926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1473127</t>
+          <t>1471255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1552898</t>
+          <t>1551496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1185846</t>
+          <t>1186599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1264732</t>
+          <t>1265050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2686983</t>
+          <t>2686973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2797652</t>
+          <t>2801574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50836</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82627</t>
+          <t>82778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67113</t>
+          <t>65882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101668</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126848</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174284</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398554</t>
+          <t>398403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430345</t>
+          <t>432184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356963</t>
+          <t>357148</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391518</t>
+          <t>392749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>765529</t>
+          <t>766312</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>812965</t>
+          <t>812131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>721725</t>
+          <t>717709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>821006</t>
+          <t>822073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1042616</t>
+          <t>1038610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1154525</t>
+          <t>1153094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1793730</t>
+          <t>1788887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1944759</t>
+          <t>1945040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2597018</t>
+          <t>2595951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2696299</t>
+          <t>2700315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2398607</t>
+          <t>2400038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2510516</t>
+          <t>2514522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5026397</t>
+          <t>5026116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5177426</t>
+          <t>5182269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>328363</t>
+          <t>329121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381874</t>
+          <t>382155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>528798</t>
+          <t>527084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>593866</t>
+          <t>590628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>878087</t>
+          <t>872266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>958231</t>
+          <t>958412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372473</t>
+          <t>372192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425984</t>
+          <t>425226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400794</t>
+          <t>404032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>465862</t>
+          <t>467576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>790776</t>
+          <t>790595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>870920</t>
+          <t>876741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>618059</t>
+          <t>617330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>708822</t>
+          <t>708852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>746579</t>
+          <t>751320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>835102</t>
+          <t>838021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1395403</t>
+          <t>1391805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1515975</t>
+          <t>1517228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1367563</t>
+          <t>1367533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1458326</t>
+          <t>1459055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1153198</t>
+          <t>1150279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1241721</t>
+          <t>1236980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2548710</t>
+          <t>2547457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2669282</t>
+          <t>2672880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105643</t>
+          <t>106215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147545</t>
+          <t>145295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>135320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177786</t>
+          <t>178153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254448</t>
+          <t>250591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312730</t>
+          <t>313396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399341</t>
+          <t>401591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441243</t>
+          <t>440671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>371354</t>
+          <t>370987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>412636</t>
+          <t>413820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>783297</t>
+          <t>782631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>841579</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1089899</t>
+          <t>1088595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1200840</t>
+          <t>1197600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1445027</t>
+          <t>1454193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1565189</t>
+          <t>1572667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2570666</t>
+          <t>2574073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2729724</t>
+          <t>2739930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2176778</t>
+          <t>2180018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2287719</t>
+          <t>2289023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1966911</t>
+          <t>1959433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2087073</t>
+          <t>2077907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4179994</t>
+          <t>4169788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4339052</t>
+          <t>4335645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>297056</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242348</t>
+          <t>275608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>283405</t>
+          <t>319875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>455086</t>
+          <t>493839</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>434511</t>
+          <t>474250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>476273</t>
+          <t>515894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>717292</t>
+          <t>790895</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686643</t>
+          <t>762561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>746146</t>
+          <t>821392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>249225</t>
+          <t>277447</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228026</t>
+          <t>254628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269083</t>
+          <t>298895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>294507</t>
+          <t>322757</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273320</t>
+          <t>300702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315082</t>
+          <t>342346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>543732</t>
+          <t>600204</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514878</t>
+          <t>569707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574381</t>
+          <t>628538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>647976</t>
+          <t>707859</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>453954</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>744729</t>
+          <t>766270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>756204</t>
+          <t>815303</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>561571</t>
+          <t>772764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>866077</t>
+          <t>860698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1404179</t>
+          <t>1523162</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1126116</t>
+          <t>1454160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1592285</t>
+          <t>1587229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1637638</t>
+          <t>1517894</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1540885</t>
+          <t>1459483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1831660</t>
+          <t>1565065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1479385</t>
+          <t>1353091</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1369512</t>
+          <t>1307696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1674018</t>
+          <t>1395630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3117023</t>
+          <t>2870985</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2928917</t>
+          <t>2806918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3395086</t>
+          <t>2939987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,27 +6223,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>151195</t>
+          <t>166663</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128283</t>
+          <t>143344</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175882</t>
+          <t>193520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>172655</t>
+          <t>196396</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155106</t>
+          <t>176775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194929</t>
+          <t>219275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>323851</t>
+          <t>363059</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295167</t>
+          <t>332513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356072</t>
+          <t>395650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -6336,22 +6336,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>494379</t>
+          <t>543795</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469692</t>
+          <t>516938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517291</t>
+          <t>567114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>487431</t>
+          <t>538093</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465157</t>
+          <t>515214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>504980</t>
+          <t>557714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>981809</t>
+          <t>1081889</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>949588</t>
+          <t>1049298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1010493</t>
+          <t>1112435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1061378</t>
+          <t>1171578</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>823313</t>
+          <t>1114665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1170032</t>
+          <t>1238218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1383945</t>
+          <t>1505538</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1163248</t>
+          <t>1454104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1509427</t>
+          <t>1562423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2445323</t>
+          <t>2677115</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2087516</t>
+          <t>2601492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2627564</t>
+          <t>2759777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2381240</t>
+          <t>2339137</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2272586</t>
+          <t>2272497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2619305</t>
+          <t>2396050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2261323</t>
+          <t>2213941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2135841</t>
+          <t>2157056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2482020</t>
+          <t>2265375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4642563</t>
+          <t>4553079</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4460322</t>
+          <t>4470417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5000370</t>
+          <t>4628702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
